--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCION 100/LTAIPT_A63F100.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCION 100/LTAIPT_A63F100.xlsx
@@ -109,28 +109,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>A755AC1FE5866ADFBD4A1D6DC10B999E</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Area_de_Transparencia/Tabla%20de%20Aplicabilidad/Tabla%20de%20Aplicabilidad.pdf</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>F579353CA8CFE5EEF234B361084C6382</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>http://cobatlaxcala.edu.mx/transparencia/TRANSPARENCIA%202022/Area_de_Transparencia/Tabla%20de%20Aplicabilidad/TABLA%20DE%20APLICABILIDAD%202022.pdf</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/04/2023</t>
   </si>
 </sst>
 </file>
@@ -526,11 +526,12 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="142.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="134.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
@@ -677,19 +678,19 @@
     </row>
     <row r="8" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>36</v>
@@ -704,7 +705,7 @@
         <v>38</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
